--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2365-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2365-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80320858-3C26-4478-8520-FB5A3FDBAFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D11AF5E-5221-4FA8-8B1F-12FA74D95B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{F988FED0-8538-4C00-8810-EF0D506020AB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{30F69EF2-AEB2-44CB-8D02-EDC3FC0472F2}"/>
   </bookViews>
   <sheets>
     <sheet name="2365-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1544,26 +1544,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36D831F9-CD6F-406A-9919-714BA89EA0DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AFCF9DA-EEFA-42B9-AC74-DB765688B55C}">
   <dimension ref="A1:X78"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1597,7 +1597,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1633,7 +1633,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1753,7 +1753,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2024</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2023</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2022</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>29</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>29</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>29</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2021</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>29</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>29</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>29</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>29</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>29</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>29</v>
       </c>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>2020</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>29</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>29</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
         <v>29</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
         <v>29</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
         <v>29</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="16" t="s">
         <v>29</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="36">
         <v>2019</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>7.71</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
         <v>29</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>7.71</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>29</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>29</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
         <v>29</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>2018</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="36">
         <v>2017</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="38">
         <v>2016</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="36">
         <v>2015</v>
       </c>
@@ -5431,7 +5431,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="38">
         <v>2014</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="36">
         <v>2013</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="38">
         <v>2012</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="36">
         <v>2011</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="38">
         <v>2010</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="36">
         <v>2009</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="38">
         <v>2008</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="36">
         <v>2007</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>32.700000000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="38">
         <v>2006</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="36">
         <v>2005</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="38">
         <v>2004</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>9.41</v>
       </c>
     </row>
-    <row r="66" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="36">
         <v>2003</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="38">
         <v>2002</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="68" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="36">
         <v>2001</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>8.18</v>
       </c>
     </row>
-    <row r="69" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="38">
         <v>2000</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="70" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="36">
         <v>1999</v>
       </c>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="38">
         <v>1998</v>
       </c>
@@ -6655,7 +6655,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="72" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="36">
         <v>1997</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="73" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="38">
         <v>1996</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="74" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="36">
         <v>1995</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A75" s="38">
         <v>1994</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A76" s="36">
         <v>1993</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A77" s="38">
         <v>1992</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A78" s="36" t="s">
         <v>68</v>
       </c>
